--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/magallanes.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1920,6 +1920,128 @@
       </c>
       <c r="M24" s="2" t="n">
         <v>38997.21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3866-124-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>69.251.300-2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>52593.26</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3866-125-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.251.300-2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>1381.53</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/magallanes.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/magallanes.xlsx
@@ -562,7 +562,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.843.130-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +948,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1013,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1078,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1143,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1241,7 +1273,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1302,7 +1338,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1363,7 +1403,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1424,7 +1468,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1485,7 +1533,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1546,7 +1598,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1607,7 +1663,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1729,7 +1789,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1790,7 +1854,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1912,7 +1980,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1973,7 +2045,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2034,7 +2110,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/magallanes.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/magallanes.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2124,6 +2124,136 @@
         <v>1381.53</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>638-151-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>61.824.000-2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>23927.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>638-152-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.824.000-2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SERVIU REGION DE MAGALLANES Y DE LA ANTARTICA CHILENA</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>945.77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
